--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/pre LAM_HRM-2031-0140/Panel-28/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/pre LAM_HRM-2031-0140/Panel-28/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.08938</v>
+        <v>16.92156</v>
       </c>
       <c r="D2" t="n">
-        <v>16.76989</v>
+        <v>16.65537</v>
       </c>
       <c r="E2" t="n">
-        <v>16.7807</v>
+        <v>16.80105</v>
       </c>
       <c r="F2" t="n">
-        <v>42.94301</v>
+        <v>42.7438</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05125</v>
+        <v>0.05151</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81447</v>
+        <v>1.83065</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.22872</v>
+        <v>16.77676</v>
       </c>
       <c r="D3" t="n">
-        <v>16.72285</v>
+        <v>16.30543</v>
       </c>
       <c r="E3" t="n">
-        <v>16.66777</v>
+        <v>16.66041</v>
       </c>
       <c r="F3" t="n">
-        <v>42.50868</v>
+        <v>41.74692</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05159</v>
+        <v>0.05046</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81695</v>
+        <v>1.83727</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.89398</v>
+        <v>16.7867</v>
       </c>
       <c r="D4" t="n">
-        <v>16.89616</v>
+        <v>16.56241</v>
       </c>
       <c r="E4" t="n">
-        <v>16.78095</v>
+        <v>16.73103</v>
       </c>
       <c r="F4" t="n">
-        <v>42.44722</v>
+        <v>42.1716</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04971</v>
+        <v>0.04967</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8175</v>
+        <v>1.8122</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.40057</v>
+        <v>16.84734</v>
       </c>
       <c r="D6" t="n">
-        <v>15.94417</v>
+        <v>15.86303</v>
       </c>
       <c r="E6" t="n">
-        <v>16.53543</v>
+        <v>16.16771</v>
       </c>
       <c r="F6" t="n">
-        <v>21.74182</v>
+        <v>22.11517</v>
       </c>
       <c r="G6" t="n">
-        <v>34.48224</v>
+        <v>34.46199</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.56241</v>
+        <v>16.43271</v>
       </c>
       <c r="D7" t="n">
-        <v>15.86455</v>
+        <v>15.98262</v>
       </c>
       <c r="E7" t="n">
-        <v>16.09273</v>
+        <v>16.32657</v>
       </c>
       <c r="F7" t="n">
-        <v>21.64575</v>
+        <v>21.36338</v>
       </c>
       <c r="G7" t="n">
-        <v>34.51152</v>
+        <v>34.64891</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.56582</v>
+        <v>16.9796</v>
       </c>
       <c r="D8" t="n">
-        <v>15.7685</v>
+        <v>15.89464</v>
       </c>
       <c r="E8" t="n">
-        <v>16.66352</v>
+        <v>16.75134</v>
       </c>
       <c r="F8" t="n">
-        <v>21.92109</v>
+        <v>21.72693</v>
       </c>
       <c r="G8" t="n">
-        <v>33.44473</v>
+        <v>34.09101</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.60693</v>
+        <v>0.61715</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1158</v>
+        <v>1.14736</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.59619</v>
+        <v>0.60343</v>
       </c>
       <c r="D11" t="n">
-        <v>1.12763</v>
+        <v>1.09135</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.61744</v>
+        <v>0.60568</v>
       </c>
       <c r="D12" t="n">
-        <v>1.10659</v>
+        <v>1.10707</v>
       </c>
     </row>
   </sheetData>
